--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486748_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486748_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3936</v>
+        <v>2.0337</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0557</v>
+        <v>2.7455</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6621</v>
+        <v>-0.7118</v>
       </c>
       <c r="G2" t="n">
         <v>-0.1942</v>
@@ -610,13 +610,13 @@
         <v>2.51</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4468</v>
+        <v>-0.8067</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2763</v>
+        <v>-0.5865</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1705</v>
+        <v>-0.2202</v>
       </c>
       <c r="V2" t="n">
         <v>2.4554</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.574</v>
+        <v>1.8884</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9028</v>
+        <v>1.3165</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6713</v>
+        <v>0.5719</v>
       </c>
       <c r="G3" t="n">
         <v>0.1231</v>
@@ -688,13 +688,13 @@
         <v>1.3515</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0993</v>
+        <v>0.4137</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4415</v>
+        <v>-0.0278</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.4415</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3612</v>
+        <v>0.386</v>
       </c>
       <c r="E4" t="n">
         <v>0.0827</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2785</v>
+        <v>0.3033</v>
       </c>
       <c r="G4" t="n">
         <v>0.3447</v>
@@ -766,13 +766,13 @@
         <v>0.1931</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1765</v>
+        <v>-0.1517</v>
       </c>
       <c r="T4" t="n">
         <v>0.0827</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2592</v>
+        <v>-0.2344</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1379</v>
+        <v>0.2413</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0552</v>
+        <v>0.0482</v>
       </c>
       <c r="F5" t="n">
         <v>0.1931</v>
@@ -844,10 +844,10 @@
         <v>0.1931</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0552</v>
+        <v>0.0482</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0552</v>
+        <v>0.0482</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5125999999999999</v>
+        <v>0.0225</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6693</v>
+        <v>0.9313</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1819</v>
+        <v>-0.9088000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>0.5476</v>
@@ -922,13 +922,13 @@
         <v>1.7377</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1696</v>
+        <v>-0.6344</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8002</v>
+        <v>-0.5382</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3694</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>1.2678</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8092</v>
+        <v>-0.9664</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0697</v>
+        <v>-0.2765</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7396</v>
+        <v>-0.6899</v>
       </c>
       <c r="G7" t="n">
         <v>-1.6697</v>
@@ -1000,13 +1000,13 @@
         <v>0.1931</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6674</v>
+        <v>0.5102</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.3723</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0883</v>
+        <v>0.138</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8721</v>
+        <v>-1.2528</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0021</v>
+        <v>0.7953</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8742</v>
+        <v>-2.0481</v>
       </c>
       <c r="G8" t="n">
         <v>0.4394</v>
@@ -1078,13 +1078,13 @@
         <v>1.3515</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2813</v>
+        <v>-0.662</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3038</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0225</v>
+        <v>-0.1513</v>
       </c>
       <c r="V8" t="n">
         <v>-0.451</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. SOW</t>
+          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3364</v>
+        <v>-2.0676</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9453</v>
+        <v>0.375</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3911</v>
+        <v>-2.4425</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.8698</v>
+        <v>-2.8747</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.1931</v>
+        <v>-1.1385</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3232</v>
+        <v>-1.7361</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2555</v>
+        <v>-0.3561</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2962</v>
+        <v>0.4486</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0407</v>
+        <v>-0.8047</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6143</v>
+        <v>-2.5186</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8969</v>
+        <v>-1.5871</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2826</v>
+        <v>-0.9314</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1931</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4853</v>
+        <v>-0.2275</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2756</v>
+        <v>-0.1451</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2098</v>
+        <v>-0.0824</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.145</v>
+        <v>1.2277</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.8415</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.145</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
+          <t>B. SOW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8882</v>
+        <v>-2.4632</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1973</v>
+        <v>-2.097</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.6908</v>
+        <v>-0.3663</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.8747</v>
+        <v>-1.8698</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1385</v>
+        <v>-2.1931</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.7361</v>
+        <v>0.3232</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3561</v>
+        <v>-1.2555</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4486</v>
+        <v>-1.2962</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.8047</v>
+        <v>0.0407</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.5186</v>
+        <v>-0.6143</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5871</v>
+        <v>-0.8969</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9314</v>
+        <v>0.2826</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1931</v>
+        <v>0.1931</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7723</v>
+        <v>1.1585</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0481</v>
+        <v>0.3585</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7174</v>
+        <v>0.1239</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3307</v>
+        <v>0.2346</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2277</v>
+        <v>-1.145</v>
       </c>
       <c r="W10" t="n">
-        <v>1.8415</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6138</v>
+        <v>-1.145</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7299</v>
+        <v>-3.3189</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2969</v>
+        <v>-3.0349</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.433</v>
+        <v>-0.284</v>
       </c>
       <c r="G11" t="n">
         <v>-6.0897</v>
@@ -1312,13 +1312,13 @@
         <v>2.51</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.418</v>
+        <v>-1.007</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1038</v>
+        <v>-0.8417</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3142</v>
+        <v>-0.1652</v>
       </c>
       <c r="V11" t="n">
         <v>1.2678</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7573</v>
+        <v>-4.7725</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.9379</v>
+        <v>-4.7793</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1806</v>
+        <v>0.0068</v>
       </c>
       <c r="G12" t="n">
         <v>-3.5907</v>
@@ -1390,13 +1390,13 @@
         <v>3.2823</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3367</v>
+        <v>-0.3519</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6902</v>
+        <v>-0.5316</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3535</v>
+        <v>0.1796</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2506</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.7805</v>
+        <v>-6.6741</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.5347</v>
+        <v>-7.1552</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7542</v>
+        <v>0.4811</v>
       </c>
       <c r="G13" t="n">
         <v>-4.9942</v>
@@ -1468,13 +1468,13 @@
         <v>3.0892</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2316</v>
+        <v>-0.6621</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0007</v>
+        <v>-0.6212</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2323</v>
+        <v>-0.0409</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2455</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-17.2195</v>
+        <v>-16.9436</v>
       </c>
       <c r="E14" t="n">
-        <v>-11.3244</v>
+        <v>-11.0484</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.895</v>
+        <v>-5.8952</v>
       </c>
       <c r="G14" t="n">
         <v>-19.8282</v>
@@ -1534,25 +1534,25 @@
         <v>-12.0756</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.5558</v>
+        <v>-4.555800000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>1.930799999999999</v>
+        <v>1.9308</v>
       </c>
       <c r="Q14" t="n">
         <v>-16.4118</v>
       </c>
       <c r="R14" t="n">
-        <v>18.34229999999999</v>
+        <v>18.3423</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.4486</v>
+        <v>-3.1727</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.4517</v>
+        <v>-3.1756</v>
       </c>
       <c r="U14" t="n">
-        <v>0.003199999999999981</v>
+        <v>0.00310000000000004</v>
       </c>
       <c r="V14" t="n">
         <v>4.1266</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.3843</v>
+        <v>7.2257</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6496</v>
+        <v>3.8565</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7347</v>
+        <v>3.3692</v>
       </c>
       <c r="G15" t="n">
         <v>4.358</v>
@@ -1624,13 +1624,13 @@
         <v>2.51</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4138</v>
+        <v>0.4276</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3866</v>
+        <v>-0.1798</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0272</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>2.8262</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.015</v>
+        <v>4.4591</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3429</v>
+        <v>1.9292</v>
       </c>
       <c r="F16" t="n">
-        <v>3.6721</v>
+        <v>2.5298</v>
       </c>
       <c r="G16" t="n">
         <v>4.4808</v>
@@ -1702,13 +1702,13 @@
         <v>1.9308</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1561</v>
+        <v>1.6001</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6891</v>
+        <v>0.2754</v>
       </c>
       <c r="U16" t="n">
-        <v>2.4669</v>
+        <v>1.3247</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6565</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.4645</v>
+        <v>4.4105</v>
       </c>
       <c r="E17" t="n">
-        <v>2.026</v>
+        <v>2.6465</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4386</v>
+        <v>1.764</v>
       </c>
       <c r="G17" t="n">
         <v>2.5275</v>
@@ -1780,13 +1780,13 @@
         <v>2.7031</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7114</v>
+        <v>0.2346</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8002</v>
+        <v>-0.1797</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0888</v>
+        <v>0.4142</v>
       </c>
       <c r="V17" t="n">
         <v>1.8415</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.2589</v>
+        <v>2.3363</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1723</v>
+        <v>-0.7929</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4313</v>
+        <v>3.1292</v>
       </c>
       <c r="G18" t="n">
         <v>2.5641</v>
@@ -1858,13 +1858,13 @@
         <v>2.8962</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2741</v>
+        <v>1.3515</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9371</v>
+        <v>0.3166</v>
       </c>
       <c r="U18" t="n">
-        <v>0.337</v>
+        <v>1.0349</v>
       </c>
       <c r="V18" t="n">
         <v>-0.6138</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.1924</v>
+        <v>1.9826</v>
       </c>
       <c r="E19" t="n">
         <v>0.166</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0264</v>
+        <v>1.8166</v>
       </c>
       <c r="G19" t="n">
         <v>1.2101</v>
@@ -1936,13 +1936,13 @@
         <v>2.1239</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7892</v>
+        <v>0.5794</v>
       </c>
       <c r="T19" t="n">
         <v>-0.0004</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7895</v>
+        <v>0.5798</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. CAULIN TORNERO</t>
+          <t>E. QUIJADA GARCÍA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3663</v>
+        <v>0.8638</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4765</v>
+        <v>-0.3124</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1101</v>
+        <v>1.1761</v>
       </c>
       <c r="G20" t="n">
-        <v>2.6275</v>
+        <v>1.2046</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2553</v>
+        <v>0.5309</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3722</v>
+        <v>0.6737</v>
       </c>
       <c r="J20" t="n">
-        <v>2.4146</v>
+        <v>0.5152</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6007</v>
+        <v>0.3932</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8138</v>
+        <v>0.1221</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2129</v>
+        <v>0.6893</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3454</v>
+        <v>0.1377</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5583</v>
+        <v>0.5516</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5792</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5446</v>
+        <v>0.5792</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0994</v>
+        <v>0.331</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0273</v>
+        <v>0.1378</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1267</v>
+        <v>0.1932</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.741</v>
+        <v>-0.2856</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.741</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3428</v>
+        <v>0.7827</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5476</v>
+        <v>0.651</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2048</v>
+        <v>0.1317</v>
       </c>
       <c r="G21" t="n">
         <v>1.8162</v>
@@ -2092,13 +2092,13 @@
         <v>0.7723</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4468</v>
+        <v>-0.0068</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1655</v>
+        <v>-0.0621</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2813</v>
+        <v>0.0553</v>
       </c>
       <c r="V21" t="n">
         <v>-1.7989</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. QUIJADA GARCÍA</t>
+          <t>A. CAULIN TORNERO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2514</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7261</v>
+        <v>1.2696</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9775</v>
+        <v>-0.6109</v>
       </c>
       <c r="G22" t="n">
-        <v>1.2046</v>
+        <v>2.6275</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5309</v>
+        <v>1.2553</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6737</v>
+        <v>1.3722</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5152</v>
+        <v>2.4146</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3932</v>
+        <v>1.6007</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1221</v>
+        <v>0.8138</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6893</v>
+        <v>0.2129</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1377</v>
+        <v>-0.3454</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5516</v>
+        <v>0.5583</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3862</v>
+        <v>0.5792</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5792</v>
+        <v>1.5446</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2814</v>
+        <v>0.193</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2759</v>
+        <v>-0.1795</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0055</v>
+        <v>0.3726</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2856</v>
+        <v>-2.741</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2856</v>
+        <v>-2.741</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0562</v>
+        <v>-4.121</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4151</v>
+        <v>-3.5185</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6411</v>
+        <v>-0.6025</v>
       </c>
       <c r="G23" t="n">
         <v>-0.9606</v>
@@ -2248,13 +2248,13 @@
         <v>1.3515</v>
       </c>
       <c r="S23" t="n">
-        <v>0.182</v>
+        <v>0.1172</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0279</v>
+        <v>-0.1313</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2099</v>
+        <v>0.2485</v>
       </c>
       <c r="V23" t="n">
         <v>-2.6984</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>17.2194</v>
+        <v>18.5985</v>
       </c>
       <c r="E24" t="n">
-        <v>5.8951</v>
+        <v>5.895000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>11.3246</v>
+        <v>12.7032</v>
       </c>
       <c r="G24" t="n">
         <v>19.8282</v>
@@ -2311,7 +2311,7 @@
         <v>3.1967</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3521000000000001</v>
+        <v>-0.3521</v>
       </c>
       <c r="O24" t="n">
         <v>3.5488</v>
@@ -2326,13 +2326,13 @@
         <v>16.4116</v>
       </c>
       <c r="S24" t="n">
-        <v>3.448599999999999</v>
+        <v>4.8276</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.002999999999999968</v>
+        <v>-0.003000000000000003</v>
       </c>
       <c r="U24" t="n">
-        <v>3.4514</v>
+        <v>4.8306</v>
       </c>
       <c r="V24" t="n">
         <v>-4.1265</v>
